--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.175.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.175.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.175.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.175.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€�&amp; c.</t>
+          <t>L22: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: 1 ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUBPNA-â€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]168</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]168</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L11: isolated marker/symbol line :: 168</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L34: symbol-only separator/garbage line :: % ___________________________-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]168</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -632,7 +636,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 51</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -666,14 +674,10 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: VACATION ..............................â€¢</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: VACATION ..............................•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L36: symbol-only separator/garbage line :: .49</t>
+          <t>L34: symbol-only separator/garbage line :: % ___________________________-</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -728,7 +732,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 51</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 51</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -740,7 +744,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 139</t>
+          <t>L36: symbol-only separator/garbage line :: .49</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -771,7 +775,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -781,11 +785,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1. At page 5, the first line should read â€œis said to deal with it" &amp;c., instead of</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L40: symbol-only separator/garbage line :: .16</t>
+          <t>L38: isolated marker/symbol line :: 139</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -836,11 +836,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: repeated periods :: Â«dealsâ€� &amp;c..</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -850,7 +846,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L42: symbol-only separator/garbage line :: .15</t>
+          <t>L40: symbol-only separator/garbage line :: .16</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -896,18 +892,18 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 51</t>
+          <t>L22: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: 1 ：</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L46: symbol-only separator/garbage line :: . 51</t>
+          <t>L42: symbol-only separator/garbage line :: .15</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: VACATION ..............................â€¢</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: VACATION ..............................•</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -947,18 +943,18 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 51</t>
+          <t>L39: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L48: symbol-only separator/garbage line :: - 52</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 51</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: repeated periods :: Â«dealsâ€� &amp;c..</t>
+          <t>L59: punctuation artifact: repeated periods :: «deals” &amp;c..</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -998,18 +994,18 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 52</t>
+          <t>L40: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L50: symbol-only separator/garbage line :: .52</t>
+          <t>L46: symbol-only separator/garbage line :: . 51</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L66: punctuation artifact: repeated periods :: instead of Â« all applications for leave" &amp;c..</t>
+          <t>L66: punctuation artifact: repeated periods :: instead of « all applications for leave" &amp;c..</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1029,12 +1025,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1049,12 +1045,12 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 52</t>
+          <t>L41: isolated marker/symbol line :: 52</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 106</t>
+          <t>L48: symbol-only separator/garbage line :: - 52</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1085,7 +1081,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1100,12 +1096,12 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 106</t>
+          <t>L43: isolated marker/symbol line :: 52</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: N</t>
+          <t>L50: symbol-only separator/garbage line :: .52</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1127,12 +1123,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1147,12 +1143,12 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 6</t>
+          <t>L44: isolated marker/symbol line :: 106</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: a</t>
+          <t>L52: isolated marker/symbol line :: 106</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1192,8 +1188,16 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
-      <c r="O13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L64: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>L90: isolated marker/symbol line :: N</t>
+        </is>
+      </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr"/>
@@ -1218,7 +1222,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1231,8 +1235,16 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
-      <c r="O14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>L83: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>L92: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
